--- a/exemplo/controle_financiamentos_exemplo.xlsx
+++ b/exemplo/controle_financiamentos_exemplo.xlsx
@@ -10,6 +10,7 @@
     <sheet name="CLIENTES" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="EQUIPAMENTOS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="PROPOSTAS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="VENDEDORES" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +485,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -530,7 +531,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -571,7 +572,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -786,7 +787,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B2">
         <f>IFERROR(VLOOKUP(C2,CLIENTES!$B:$C,2,FALSE()),"")</f>
@@ -834,7 +835,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B3">
         <f>IFERROR(VLOOKUP(C3,CLIENTES!$B:$C,2,FALSE()),"")</f>
@@ -878,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B4">
         <f>IFERROR(VLOOKUP(C4,CLIENTES!$B:$C,2,FALSE()),"")</f>
@@ -921,6 +922,34 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Negado na pré-análise (exemplo)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>NOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vendedor Exemplo</t>
         </is>
       </c>
     </row>

--- a/exemplo/controle_financiamentos_exemplo.xlsx
+++ b/exemplo/controle_financiamentos_exemplo.xlsx
@@ -53,9 +53,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -423,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,28 +465,78 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>ENDEREÇO</t>
+          <t>CEP</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>LOGRADOURO</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NÚMERO</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>COMPLEMENTO</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>BAIRRO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>CIDADE</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ENDEREÇO (REVISAR)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>VINCULADO</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>REDE SOCIAL</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>NOME DO PAI</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>NOME DA MÃE</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>PROFISSÃO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46280</v>
+      <c r="A2" s="3" t="n">
+        <v>46284</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -507,31 +558,78 @@
           <t>MARIA EXEMPLO DA SILVA</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
+      <c r="F2" s="3" t="n">
+        <v>31121</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>(11) 91234-5678</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Rua Fictícia, 123 - Bairro Exemplo - Cidade/UF</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>01001-000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Rua Fictícia</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>apto 45</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Bairro Exemplo</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Cidade Exemplo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>@maria.exemplo</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>maria.exemplo@email.com</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Pai Exemplo da Silva</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Mãe Exemplo da Silva</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Profissão Exemplo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46280</v>
+      <c r="A3" s="3" t="n">
+        <v>46284</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -553,26 +651,51 @@
           <t>JOÃO EXEMPLO SOUZA</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
+      <c r="F3" s="3" t="n"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>(21) 98888-7777</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Avenida Modelo, 456 - Bairro Teste - Cidade/UF</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>20000-000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Avenida Modelo</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Bairro Teste</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Cidade Teste</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>RJ</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>joao.exemplo@email.com</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46280</v>
+      <c r="A4" s="3" t="n">
+        <v>46284</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -594,23 +717,25 @@
           <t>ANA EXEMPLO COSTA</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
+      <c r="F4" s="3" t="n"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>(31) 97777-6666</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Praça Amostra, 789 - Bairro Fake - Cidade/UF</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Praça Amostra, 789 apto 12 - Bairro Fake - Cidade/UF</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Maria Exemplo da Silva</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>ana.exemplo@email.com</t>
         </is>
@@ -676,10 +801,10 @@
       <c r="C2" t="n">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>2500</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>65000</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -702,10 +827,10 @@
       <c r="C3" t="n">
         <v>24</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>1800</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>35000</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -786,8 +911,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46280</v>
+      <c r="A2" s="3" t="n">
+        <v>46284</v>
       </c>
       <c r="B2">
         <f>IFERROR(VLOOKUP(C2,CLIENTES!$B:$C,2,FALSE()),"")</f>
@@ -802,7 +927,7 @@
         <f>IFERROR(VLOOKUP(C2,CLIENTES!$B:$E,4,FALSE()),"")</f>
         <v/>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>65000</v>
       </c>
       <c r="F2" t="n">
@@ -819,7 +944,7 @@
         </is>
       </c>
       <c r="I2">
-        <f>IF(A2="","",IF(OR(UPPER(J2)="APROVADO",UPPER(J2)="NEGADO"),"Encerrado",TODAY()-A2&amp;" dias"))</f>
+        <f>IF(A2="","",IF(OR(UPPER(J2)="APROVADO",UPPER(J2)="CANCELADA",UPPER(J2)="CANCELADO",UPPER(J2)="NEGADA",UPPER(J2)="NEGADO",UPPER(J2)="REPROVADA",UPPER(J2)="REPROVADO"),"Encerrado",TODAY()-A2&amp;" dias"))</f>
         <v/>
       </c>
       <c r="J2" t="inlineStr">
@@ -834,8 +959,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46280</v>
+      <c r="A3" s="3" t="n">
+        <v>46284</v>
       </c>
       <c r="B3">
         <f>IFERROR(VLOOKUP(C3,CLIENTES!$B:$C,2,FALSE()),"")</f>
@@ -850,7 +975,7 @@
         <f>IFERROR(VLOOKUP(C3,CLIENTES!$B:$E,4,FALSE()),"")</f>
         <v/>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>35000</v>
       </c>
       <c r="F3" t="n">
@@ -867,7 +992,7 @@
         </is>
       </c>
       <c r="I3">
-        <f>IF(A3="","",IF(OR(UPPER(J3)="APROVADO",UPPER(J3)="NEGADO"),"Encerrado",TODAY()-A3&amp;" dias"))</f>
+        <f>IF(A3="","",IF(OR(UPPER(J3)="APROVADO",UPPER(J3)="CANCELADA",UPPER(J3)="CANCELADO",UPPER(J3)="NEGADA",UPPER(J3)="NEGADO",UPPER(J3)="REPROVADA",UPPER(J3)="REPROVADO"),"Encerrado",TODAY()-A3&amp;" dias"))</f>
         <v/>
       </c>
       <c r="J3" t="inlineStr">
@@ -878,8 +1003,8 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46280</v>
+      <c r="A4" s="3" t="n">
+        <v>46284</v>
       </c>
       <c r="B4">
         <f>IFERROR(VLOOKUP(C4,CLIENTES!$B:$C,2,FALSE()),"")</f>
@@ -894,7 +1019,7 @@
         <f>IFERROR(VLOOKUP(C4,CLIENTES!$B:$E,4,FALSE()),"")</f>
         <v/>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>40000</v>
       </c>
       <c r="F4" t="n">
@@ -911,7 +1036,7 @@
         </is>
       </c>
       <c r="I4">
-        <f>IF(A4="","",IF(OR(UPPER(J4)="APROVADO",UPPER(J4)="NEGADO"),"Encerrado",TODAY()-A4&amp;" dias"))</f>
+        <f>IF(A4="","",IF(OR(UPPER(J4)="APROVADO",UPPER(J4)="CANCELADA",UPPER(J4)="CANCELADO",UPPER(J4)="NEGADA",UPPER(J4)="NEGADO",UPPER(J4)="REPROVADA",UPPER(J4)="REPROVADO"),"Encerrado",TODAY()-A4&amp;" dias"))</f>
         <v/>
       </c>
       <c r="J4" t="inlineStr">
@@ -936,7 +1061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,6 +1070,16 @@
           <t>NOME</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SENHA_HASH</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SALT</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
